--- a/TRACKER IDM.xlsx
+++ b/TRACKER IDM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domenica.villalva.01\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD516625-7C9A-4DBA-AA9C-BF01D77811F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C46C71C-A728-4CA4-BA92-FC9E76FB85E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6D1496F6-952A-45C4-9276-C735DD240041}"/>
   </bookViews>
@@ -24,9 +24,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId5"/>
-    <pivotCache cacheId="5" r:id="rId6"/>
-    <pivotCache cacheId="6" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="333">
   <si>
     <t>AÑO</t>
   </si>
@@ -14793,270 +14793,13 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B64F7D33-69A2-45A5-AF31-5F26051480F8}" name="TablaDinámica2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
-  <location ref="B12:C17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{97318CE9-5551-4A15-AE7A-DEB6EF67B650}" name="TablaDinámica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="19">
+  <location ref="B52:C56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de ENCARGADO" fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C428002-B46E-49F3-8903-DBE5024210CB}" name="TablaDinámica10" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="G3:H21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="18">
-        <item x="4"/>
-        <item x="12"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="14"/>
-        <item x="13"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="18">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de MINI PROYECTO" fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A5ABEC2-16E8-4C32-9965-73ECB329E04D}" name="TablaDinámica3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
-  <location ref="B21:C26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de EQUIPO DE SOPORTE" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2ADA225C-1E53-4E5F-9D05-21CB4FE87226}" name="TablaDinámica5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="15">
-  <location ref="B41:C46" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="84">
+      <items count="87">
         <item x="12"/>
         <item x="43"/>
         <item x="40"/>
@@ -15140,6 +14883,9 @@
         <item x="51"/>
         <item x="15"/>
         <item x="37"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -15148,8 +14894,8 @@
       <items count="6">
         <item h="1" x="2"/>
         <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
         <item h="1" x="4"/>
         <item t="default"/>
       </items>
@@ -15170,18 +14916,15 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="4">
     <i>
-      <x v="17"/>
+      <x v="83"/>
     </i>
     <i>
-      <x v="18"/>
+      <x v="84"/>
     </i>
     <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="33"/>
+      <x v="85"/>
     </i>
     <i t="grand">
       <x/>
@@ -15197,7 +14940,7 @@
   <dataFields count="1">
     <dataField name="Cuenta de PROYECTO" fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="3">
+  <chartFormats count="5">
     <chartFormat chart="3" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -15225,6 +14968,24 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="15" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -15238,8 +14999,455 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C23A92F5-1981-4887-B0C5-8FF651EA6FB2}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="3">
+  <location ref="B30:C35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cuenta de ESTADO" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B092A96F-817F-4509-A8B6-4C9CC6DFF2D8}" name="TablaDinámica8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="29">
+  <location ref="B71:C72" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="87">
+        <item x="12"/>
+        <item x="43"/>
+        <item x="40"/>
+        <item x="30"/>
+        <item x="17"/>
+        <item x="32"/>
+        <item x="16"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="31"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="46"/>
+        <item x="42"/>
+        <item x="29"/>
+        <item x="45"/>
+        <item x="23"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="24"/>
+        <item x="38"/>
+        <item x="44"/>
+        <item x="48"/>
+        <item x="28"/>
+        <item x="49"/>
+        <item x="47"/>
+        <item x="11"/>
+        <item x="27"/>
+        <item x="13"/>
+        <item x="68"/>
+        <item x="14"/>
+        <item x="19"/>
+        <item x="9"/>
+        <item x="39"/>
+        <item x="66"/>
+        <item x="26"/>
+        <item x="41"/>
+        <item x="80"/>
+        <item x="70"/>
+        <item x="75"/>
+        <item x="77"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="76"/>
+        <item x="79"/>
+        <item x="71"/>
+        <item x="81"/>
+        <item x="69"/>
+        <item x="78"/>
+        <item x="74"/>
+        <item x="67"/>
+        <item x="82"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="62"/>
+        <item x="53"/>
+        <item x="52"/>
+        <item x="8"/>
+        <item x="63"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="50"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="64"/>
+        <item x="54"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="59"/>
+        <item x="58"/>
+        <item x="0"/>
+        <item x="65"/>
+        <item x="51"/>
+        <item x="15"/>
+        <item x="37"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="1">
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="4" hier="-1"/>
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de PROYECTO" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="10">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="15" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B64F7D33-69A2-45A5-AF31-5F26051480F8}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
+  <location ref="B12:C17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cuenta de ENCARGADO" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4EE35FED-4484-4582-B7BB-D4518F2C116D}" name="TablaDinámica7" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="23">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A5ABEC2-16E8-4C32-9965-73ECB329E04D}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
+  <location ref="B21:C26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cuenta de EQUIPO DE SOPORTE" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4EE35FED-4484-4582-B7BB-D4518F2C116D}" name="TablaDinámica7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="23">
   <location ref="B62:C65" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -15460,8 +15668,174 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{509FABA1-A24F-4906-A66E-E889D6D47B6A}" name="TablaDinámica9" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="33">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C428002-B46E-49F3-8903-DBE5024210CB}" name="TablaDinámica10" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="G3:H21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="18">
+        <item x="4"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="18">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cuenta de MINI PROYECTO" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05D62250-297F-4B20-8F01-25B81C5C2A31}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
+  <location ref="B3:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cuenta de TIPO" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{509FABA1-A24F-4906-A66E-E889D6D47B6A}" name="TablaDinámica9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="33">
   <location ref="B78:C80" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -15724,14 +16098,22 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{97318CE9-5551-4A15-AE7A-DEB6EF67B650}" name="TablaDinámica6" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="19">
-  <location ref="B52:C56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2ADA225C-1E53-4E5F-9D05-21CB4FE87226}" name="TablaDinámica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="15">
+  <location ref="B41:C46" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="87">
+      <items count="84">
         <item x="12"/>
         <item x="43"/>
         <item x="40"/>
@@ -15815,9 +16197,6 @@
         <item x="51"/>
         <item x="15"/>
         <item x="37"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -15826,8 +16205,8 @@
       <items count="6">
         <item h="1" x="2"/>
         <item h="1" x="3"/>
-        <item x="0"/>
-        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
         <item h="1" x="4"/>
         <item t="default"/>
       </items>
@@ -15848,15 +16227,18 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="5">
     <i>
-      <x v="83"/>
+      <x v="17"/>
     </i>
     <i>
-      <x v="84"/>
+      <x v="18"/>
     </i>
     <i>
-      <x v="85"/>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="33"/>
     </i>
     <i t="grand">
       <x/>
@@ -15872,7 +16254,7 @@
   <dataFields count="1">
     <dataField name="Cuenta de PROYECTO" fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="3">
     <chartFormat chart="3" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -15892,388 +16274,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="11" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="15" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05D62250-297F-4B20-8F01-25B81C5C2A31}" name="TablaDinámica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0">
-  <location ref="B3:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de TIPO" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C23A92F5-1981-4887-B0C5-8FF651EA6FB2}" name="TablaDinámica4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="3">
-  <location ref="B30:C35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de ESTADO" fld="6" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B092A96F-817F-4509-A8B6-4C9CC6DFF2D8}" name="TablaDinámica8" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="29">
-  <location ref="B71:C72" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="87">
-        <item x="12"/>
-        <item x="43"/>
-        <item x="40"/>
-        <item x="30"/>
-        <item x="17"/>
-        <item x="32"/>
-        <item x="16"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="31"/>
-        <item x="20"/>
-        <item x="18"/>
-        <item x="46"/>
-        <item x="42"/>
-        <item x="29"/>
-        <item x="45"/>
-        <item x="23"/>
-        <item x="34"/>
-        <item x="33"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="24"/>
-        <item x="38"/>
-        <item x="44"/>
-        <item x="48"/>
-        <item x="28"/>
-        <item x="49"/>
-        <item x="47"/>
-        <item x="11"/>
-        <item x="27"/>
-        <item x="13"/>
-        <item x="68"/>
-        <item x="14"/>
-        <item x="19"/>
-        <item x="9"/>
-        <item x="39"/>
-        <item x="66"/>
-        <item x="26"/>
-        <item x="41"/>
-        <item x="80"/>
-        <item x="70"/>
-        <item x="75"/>
-        <item x="77"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="76"/>
-        <item x="79"/>
-        <item x="71"/>
-        <item x="81"/>
-        <item x="69"/>
-        <item x="78"/>
-        <item x="74"/>
-        <item x="67"/>
-        <item x="82"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="62"/>
-        <item x="53"/>
-        <item x="52"/>
-        <item x="8"/>
-        <item x="63"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="50"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="64"/>
-        <item x="54"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="59"/>
-        <item x="58"/>
-        <item x="0"/>
-        <item x="65"/>
-        <item x="51"/>
-        <item x="15"/>
-        <item x="37"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="6">
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="6">
-        <item h="1" x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="1">
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="4" hier="-1"/>
-    <pageField fld="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de PROYECTO" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="10">
-    <chartFormat chart="3" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="15" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="19" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="23" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="26" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -17022,7 +17022,7 @@
         <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K12" s="11"/>
     </row>
@@ -17043,7 +17043,7 @@
         <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K13" s="11"/>
     </row>
@@ -17066,6 +17066,9 @@
       <c r="H14" t="s">
         <v>36</v>
       </c>
+      <c r="I14" t="s">
+        <v>38</v>
+      </c>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -17085,7 +17088,7 @@
         <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K15" s="11"/>
     </row>
@@ -17108,6 +17111,9 @@
       <c r="H16" t="s">
         <v>36</v>
       </c>
+      <c r="I16" t="s">
+        <v>38</v>
+      </c>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -17129,6 +17135,9 @@
       <c r="H17" t="s">
         <v>19</v>
       </c>
+      <c r="I17" t="s">
+        <v>38</v>
+      </c>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -17226,7 +17235,7 @@
         <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K21" s="11"/>
     </row>
@@ -17376,7 +17385,7 @@
         <v>20</v>
       </c>
       <c r="I27" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J27" s="3">
         <v>0.5</v>
@@ -17475,7 +17484,7 @@
         <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J31" s="3">
         <v>0.9</v>
@@ -17577,7 +17586,7 @@
         <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K35" s="11"/>
     </row>
@@ -17598,7 +17607,7 @@
         <v>20</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K36" s="11"/>
     </row>
@@ -19068,7 +19077,7 @@
         <v>20</v>
       </c>
       <c r="I88" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K88" s="11"/>
     </row>
@@ -19185,7 +19194,7 @@
         <v>21</v>
       </c>
       <c r="I93" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K93" s="11"/>
     </row>
@@ -19230,7 +19239,7 @@
         <v>21</v>
       </c>
       <c r="I95" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K95" s="11"/>
     </row>
@@ -19275,7 +19284,7 @@
         <v>19</v>
       </c>
       <c r="I97" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K97" s="11"/>
     </row>
@@ -19320,7 +19329,7 @@
         <v>20</v>
       </c>
       <c r="I99" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K99" s="11"/>
     </row>
@@ -19341,7 +19350,7 @@
         <v>20</v>
       </c>
       <c r="I100" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K100" s="11"/>
     </row>
@@ -19362,7 +19371,7 @@
         <v>20</v>
       </c>
       <c r="I101" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K101" s="11"/>
     </row>
@@ -19383,7 +19392,7 @@
         <v>20</v>
       </c>
       <c r="I102" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K102" s="11"/>
     </row>
@@ -19404,7 +19413,7 @@
         <v>20</v>
       </c>
       <c r="I103" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K103" s="11"/>
     </row>
@@ -19422,7 +19431,7 @@
         <v>20</v>
       </c>
       <c r="I104" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K104" s="11"/>
     </row>
@@ -19443,7 +19452,7 @@
         <v>21</v>
       </c>
       <c r="I105" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K105" s="11"/>
     </row>
@@ -19461,7 +19470,7 @@
         <v>19</v>
       </c>
       <c r="I106" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K106" s="11"/>
     </row>
@@ -19479,7 +19488,7 @@
         <v>20</v>
       </c>
       <c r="I107" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K107" s="11"/>
     </row>
@@ -20730,7 +20739,7 @@
         <v>20</v>
       </c>
       <c r="I150" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J150">
         <v>1</v>
@@ -20910,10 +20919,10 @@
         <v>20</v>
       </c>
       <c r="I156" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J156">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K156" s="11">
         <v>46161</v>
@@ -22322,7 +22331,7 @@
           <x14:formula1>
             <xm:f>Listas!$C$2:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H88:H91 I2:I213 G214:G1048576</xm:sqref>
+          <xm:sqref>H88:H91 G214:G1048576 I2:I213</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4DD68AD0-F0B9-49E0-BFFF-79879A7125A8}">
           <x14:formula1>
